--- a/results/pr_AstroSync/exp/19VB/cv_scores/qm_rec_calib.xlsx
+++ b/results/pr_AstroSync/exp/19VB/cv_scores/qm_rec_calib.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X169"/>
+  <dimension ref="A1:Z169"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -537,6 +537,16 @@
           <t>fs</t>
         </is>
       </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>features_type</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>spectral_freqs</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -623,6 +633,16 @@
       <c r="X2" t="n">
         <v>1000</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>csp</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -709,6 +729,16 @@
       <c r="X3" t="n">
         <v>1000</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>csp</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -795,6 +825,16 @@
       <c r="X4" t="n">
         <v>1000</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>csp</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -881,6 +921,16 @@
       <c r="X5" t="n">
         <v>1000</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>csp</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -967,6 +1017,16 @@
       <c r="X6" t="n">
         <v>1000</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>csp</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1053,6 +1113,16 @@
       <c r="X7" t="n">
         <v>1000</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>csp</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1139,6 +1209,16 @@
       <c r="X8" t="n">
         <v>1000</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>csp</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1225,6 +1305,16 @@
       <c r="X9" t="n">
         <v>1000</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>csp</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1311,6 +1401,16 @@
       <c r="X10" t="n">
         <v>1000</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>csp</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1397,6 +1497,16 @@
       <c r="X11" t="n">
         <v>1000</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>csp</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1483,6 +1593,16 @@
       <c r="X12" t="n">
         <v>1000</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>csp</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1569,6 +1689,16 @@
       <c r="X13" t="n">
         <v>1000</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>csp</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1655,6 +1785,16 @@
       <c r="X14" t="n">
         <v>1000</v>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>csp</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1741,6 +1881,16 @@
       <c r="X15" t="n">
         <v>1000</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>csp</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1827,6 +1977,16 @@
       <c r="X16" t="n">
         <v>1000</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>csp</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1913,6 +2073,16 @@
       <c r="X17" t="n">
         <v>1000</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>csp</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1999,6 +2169,16 @@
       <c r="X18" t="n">
         <v>1000</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>csp</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2085,6 +2265,16 @@
       <c r="X19" t="n">
         <v>1000</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>csp</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2171,6 +2361,16 @@
       <c r="X20" t="n">
         <v>1000</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>csp</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2257,6 +2457,16 @@
       <c r="X21" t="n">
         <v>1000</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>csp</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2343,6 +2553,16 @@
       <c r="X22" t="n">
         <v>1000</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>csp</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2429,6 +2649,16 @@
       <c r="X23" t="n">
         <v>1000</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>csp</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2515,6 +2745,16 @@
       <c r="X24" t="n">
         <v>1000</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>csp</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2601,6 +2841,16 @@
       <c r="X25" t="n">
         <v>1000</v>
       </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>csp</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2687,6 +2937,16 @@
       <c r="X26" t="n">
         <v>1000</v>
       </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>csp</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2773,6 +3033,16 @@
       <c r="X27" t="n">
         <v>1000</v>
       </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>csp</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2859,6 +3129,16 @@
       <c r="X28" t="n">
         <v>1000</v>
       </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>csp</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2945,6 +3225,16 @@
       <c r="X29" t="n">
         <v>1000</v>
       </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>csp</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -3031,6 +3321,16 @@
       <c r="X30" t="n">
         <v>1000</v>
       </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>csp</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -3117,6 +3417,16 @@
       <c r="X31" t="n">
         <v>1000</v>
       </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>csp</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -3203,6 +3513,16 @@
       <c r="X32" t="n">
         <v>1000</v>
       </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>csp</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -3289,6 +3609,16 @@
       <c r="X33" t="n">
         <v>1000</v>
       </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>csp</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -3375,6 +3705,16 @@
       <c r="X34" t="n">
         <v>1000</v>
       </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>csp</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -3461,6 +3801,16 @@
       <c r="X35" t="n">
         <v>1000</v>
       </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>csp</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -3547,6 +3897,16 @@
       <c r="X36" t="n">
         <v>1000</v>
       </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>csp</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -3633,6 +3993,16 @@
       <c r="X37" t="n">
         <v>1000</v>
       </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>csp</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -3719,6 +4089,16 @@
       <c r="X38" t="n">
         <v>1000</v>
       </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>csp</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -3805,6 +4185,16 @@
       <c r="X39" t="n">
         <v>1000</v>
       </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>csp</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -3891,6 +4281,16 @@
       <c r="X40" t="n">
         <v>1000</v>
       </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>csp</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -3977,6 +4377,16 @@
       <c r="X41" t="n">
         <v>1000</v>
       </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>csp</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -4063,6 +4473,16 @@
       <c r="X42" t="n">
         <v>1000</v>
       </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>csp</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -4149,6 +4569,16 @@
       <c r="X43" t="n">
         <v>1000</v>
       </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>csp</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -4235,6 +4665,16 @@
       <c r="X44" t="n">
         <v>1000</v>
       </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>csp</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -4321,6 +4761,16 @@
       <c r="X45" t="n">
         <v>1000</v>
       </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>csp</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -4407,6 +4857,16 @@
       <c r="X46" t="n">
         <v>1000</v>
       </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>csp</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -4493,6 +4953,16 @@
       <c r="X47" t="n">
         <v>1000</v>
       </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>csp</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -4579,6 +5049,16 @@
       <c r="X48" t="n">
         <v>1000</v>
       </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>csp</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -4665,6 +5145,16 @@
       <c r="X49" t="n">
         <v>1000</v>
       </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>csp</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -4751,6 +5241,16 @@
       <c r="X50" t="n">
         <v>1000</v>
       </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>csp</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -4837,6 +5337,16 @@
       <c r="X51" t="n">
         <v>1000</v>
       </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>csp</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -4923,6 +5433,16 @@
       <c r="X52" t="n">
         <v>1000</v>
       </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>csp</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -5009,6 +5529,16 @@
       <c r="X53" t="n">
         <v>1000</v>
       </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>csp</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -5095,6 +5625,16 @@
       <c r="X54" t="n">
         <v>1000</v>
       </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>csp</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -5181,6 +5721,16 @@
       <c r="X55" t="n">
         <v>1000</v>
       </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>csp</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -5267,6 +5817,16 @@
       <c r="X56" t="n">
         <v>1000</v>
       </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>csp</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -5353,6 +5913,16 @@
       <c r="X57" t="n">
         <v>1000</v>
       </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>csp</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -5439,6 +6009,16 @@
       <c r="X58" t="n">
         <v>1000</v>
       </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>csp</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -5525,6 +6105,16 @@
       <c r="X59" t="n">
         <v>1000</v>
       </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>csp</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -5611,6 +6201,16 @@
       <c r="X60" t="n">
         <v>1000</v>
       </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>csp</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -5697,6 +6297,16 @@
       <c r="X61" t="n">
         <v>1000</v>
       </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>csp</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -5783,6 +6393,16 @@
       <c r="X62" t="n">
         <v>1000</v>
       </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>csp</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -5869,6 +6489,16 @@
       <c r="X63" t="n">
         <v>1000</v>
       </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>csp</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -5955,6 +6585,16 @@
       <c r="X64" t="n">
         <v>1000</v>
       </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>csp</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -6041,6 +6681,16 @@
       <c r="X65" t="n">
         <v>1000</v>
       </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>csp</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -6127,6 +6777,16 @@
       <c r="X66" t="n">
         <v>1000</v>
       </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>csp</t>
+        </is>
+      </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -6213,6 +6873,16 @@
       <c r="X67" t="n">
         <v>1000</v>
       </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>csp</t>
+        </is>
+      </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -6299,6 +6969,16 @@
       <c r="X68" t="n">
         <v>1000</v>
       </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>csp</t>
+        </is>
+      </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -6385,6 +7065,16 @@
       <c r="X69" t="n">
         <v>1000</v>
       </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>csp</t>
+        </is>
+      </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -6471,6 +7161,16 @@
       <c r="X70" t="n">
         <v>1000</v>
       </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>csp</t>
+        </is>
+      </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -6557,6 +7257,16 @@
       <c r="X71" t="n">
         <v>1000</v>
       </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>csp</t>
+        </is>
+      </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -6643,6 +7353,16 @@
       <c r="X72" t="n">
         <v>1000</v>
       </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>csp</t>
+        </is>
+      </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -6729,6 +7449,16 @@
       <c r="X73" t="n">
         <v>1000</v>
       </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>csp</t>
+        </is>
+      </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -6815,6 +7545,16 @@
       <c r="X74" t="n">
         <v>1000</v>
       </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>csp</t>
+        </is>
+      </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -6901,6 +7641,16 @@
       <c r="X75" t="n">
         <v>1000</v>
       </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>csp</t>
+        </is>
+      </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -6987,6 +7737,16 @@
       <c r="X76" t="n">
         <v>1000</v>
       </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>csp</t>
+        </is>
+      </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -7073,6 +7833,16 @@
       <c r="X77" t="n">
         <v>1000</v>
       </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>csp</t>
+        </is>
+      </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -7159,6 +7929,16 @@
       <c r="X78" t="n">
         <v>1000</v>
       </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>csp</t>
+        </is>
+      </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -7245,6 +8025,16 @@
       <c r="X79" t="n">
         <v>1000</v>
       </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>csp</t>
+        </is>
+      </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -7331,6 +8121,16 @@
       <c r="X80" t="n">
         <v>1000</v>
       </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>csp</t>
+        </is>
+      </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -7417,6 +8217,16 @@
       <c r="X81" t="n">
         <v>1000</v>
       </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>csp</t>
+        </is>
+      </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -7503,6 +8313,16 @@
       <c r="X82" t="n">
         <v>1000</v>
       </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>csp</t>
+        </is>
+      </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -7589,6 +8409,16 @@
       <c r="X83" t="n">
         <v>1000</v>
       </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>csp</t>
+        </is>
+      </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -7675,6 +8505,16 @@
       <c r="X84" t="n">
         <v>1000</v>
       </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>csp</t>
+        </is>
+      </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -7761,6 +8601,16 @@
       <c r="X85" t="n">
         <v>1000</v>
       </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>csp</t>
+        </is>
+      </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -7847,6 +8697,16 @@
       <c r="X86" t="n">
         <v>1000</v>
       </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>csp</t>
+        </is>
+      </c>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -7933,6 +8793,16 @@
       <c r="X87" t="n">
         <v>1000</v>
       </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>csp</t>
+        </is>
+      </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -8019,6 +8889,16 @@
       <c r="X88" t="n">
         <v>1000</v>
       </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>csp</t>
+        </is>
+      </c>
+      <c r="Z88" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -8105,6 +8985,16 @@
       <c r="X89" t="n">
         <v>1000</v>
       </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>csp</t>
+        </is>
+      </c>
+      <c r="Z89" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -8191,6 +9081,16 @@
       <c r="X90" t="n">
         <v>1000</v>
       </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>csp</t>
+        </is>
+      </c>
+      <c r="Z90" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -8277,6 +9177,16 @@
       <c r="X91" t="n">
         <v>1000</v>
       </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>csp</t>
+        </is>
+      </c>
+      <c r="Z91" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -8363,6 +9273,16 @@
       <c r="X92" t="n">
         <v>1000</v>
       </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>csp</t>
+        </is>
+      </c>
+      <c r="Z92" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -8449,6 +9369,16 @@
       <c r="X93" t="n">
         <v>1000</v>
       </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>csp</t>
+        </is>
+      </c>
+      <c r="Z93" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -8535,6 +9465,16 @@
       <c r="X94" t="n">
         <v>1000</v>
       </c>
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t>csp</t>
+        </is>
+      </c>
+      <c r="Z94" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -8621,6 +9561,16 @@
       <c r="X95" t="n">
         <v>1000</v>
       </c>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>csp</t>
+        </is>
+      </c>
+      <c r="Z95" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -8707,6 +9657,16 @@
       <c r="X96" t="n">
         <v>1000</v>
       </c>
+      <c r="Y96" t="inlineStr">
+        <is>
+          <t>csp</t>
+        </is>
+      </c>
+      <c r="Z96" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -8793,6 +9753,16 @@
       <c r="X97" t="n">
         <v>1000</v>
       </c>
+      <c r="Y97" t="inlineStr">
+        <is>
+          <t>csp</t>
+        </is>
+      </c>
+      <c r="Z97" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -8879,6 +9849,16 @@
       <c r="X98" t="n">
         <v>1000</v>
       </c>
+      <c r="Y98" t="inlineStr">
+        <is>
+          <t>csp</t>
+        </is>
+      </c>
+      <c r="Z98" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -8965,6 +9945,16 @@
       <c r="X99" t="n">
         <v>1000</v>
       </c>
+      <c r="Y99" t="inlineStr">
+        <is>
+          <t>csp</t>
+        </is>
+      </c>
+      <c r="Z99" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -9051,6 +10041,16 @@
       <c r="X100" t="n">
         <v>1000</v>
       </c>
+      <c r="Y100" t="inlineStr">
+        <is>
+          <t>csp</t>
+        </is>
+      </c>
+      <c r="Z100" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -9137,6 +10137,16 @@
       <c r="X101" t="n">
         <v>1000</v>
       </c>
+      <c r="Y101" t="inlineStr">
+        <is>
+          <t>csp</t>
+        </is>
+      </c>
+      <c r="Z101" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -9223,6 +10233,16 @@
       <c r="X102" t="n">
         <v>1000</v>
       </c>
+      <c r="Y102" t="inlineStr">
+        <is>
+          <t>csp</t>
+        </is>
+      </c>
+      <c r="Z102" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -9309,6 +10329,16 @@
       <c r="X103" t="n">
         <v>1000</v>
       </c>
+      <c r="Y103" t="inlineStr">
+        <is>
+          <t>csp</t>
+        </is>
+      </c>
+      <c r="Z103" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -9395,6 +10425,16 @@
       <c r="X104" t="n">
         <v>1000</v>
       </c>
+      <c r="Y104" t="inlineStr">
+        <is>
+          <t>csp</t>
+        </is>
+      </c>
+      <c r="Z104" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -9481,6 +10521,16 @@
       <c r="X105" t="n">
         <v>1000</v>
       </c>
+      <c r="Y105" t="inlineStr">
+        <is>
+          <t>csp</t>
+        </is>
+      </c>
+      <c r="Z105" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -9567,6 +10617,16 @@
       <c r="X106" t="n">
         <v>1000</v>
       </c>
+      <c r="Y106" t="inlineStr">
+        <is>
+          <t>csp</t>
+        </is>
+      </c>
+      <c r="Z106" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -9653,6 +10713,16 @@
       <c r="X107" t="n">
         <v>1000</v>
       </c>
+      <c r="Y107" t="inlineStr">
+        <is>
+          <t>csp</t>
+        </is>
+      </c>
+      <c r="Z107" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -9739,6 +10809,16 @@
       <c r="X108" t="n">
         <v>1000</v>
       </c>
+      <c r="Y108" t="inlineStr">
+        <is>
+          <t>csp</t>
+        </is>
+      </c>
+      <c r="Z108" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -9825,6 +10905,16 @@
       <c r="X109" t="n">
         <v>1000</v>
       </c>
+      <c r="Y109" t="inlineStr">
+        <is>
+          <t>csp</t>
+        </is>
+      </c>
+      <c r="Z109" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -9911,6 +11001,16 @@
       <c r="X110" t="n">
         <v>1000</v>
       </c>
+      <c r="Y110" t="inlineStr">
+        <is>
+          <t>csp</t>
+        </is>
+      </c>
+      <c r="Z110" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -9997,6 +11097,16 @@
       <c r="X111" t="n">
         <v>1000</v>
       </c>
+      <c r="Y111" t="inlineStr">
+        <is>
+          <t>csp</t>
+        </is>
+      </c>
+      <c r="Z111" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -10083,6 +11193,16 @@
       <c r="X112" t="n">
         <v>1000</v>
       </c>
+      <c r="Y112" t="inlineStr">
+        <is>
+          <t>csp</t>
+        </is>
+      </c>
+      <c r="Z112" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -10169,6 +11289,16 @@
       <c r="X113" t="n">
         <v>1000</v>
       </c>
+      <c r="Y113" t="inlineStr">
+        <is>
+          <t>csp</t>
+        </is>
+      </c>
+      <c r="Z113" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -10255,6 +11385,16 @@
       <c r="X114" t="n">
         <v>1000</v>
       </c>
+      <c r="Y114" t="inlineStr">
+        <is>
+          <t>csp</t>
+        </is>
+      </c>
+      <c r="Z114" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -10341,6 +11481,16 @@
       <c r="X115" t="n">
         <v>1000</v>
       </c>
+      <c r="Y115" t="inlineStr">
+        <is>
+          <t>csp</t>
+        </is>
+      </c>
+      <c r="Z115" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -10427,6 +11577,16 @@
       <c r="X116" t="n">
         <v>1000</v>
       </c>
+      <c r="Y116" t="inlineStr">
+        <is>
+          <t>csp</t>
+        </is>
+      </c>
+      <c r="Z116" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -10513,6 +11673,16 @@
       <c r="X117" t="n">
         <v>1000</v>
       </c>
+      <c r="Y117" t="inlineStr">
+        <is>
+          <t>csp</t>
+        </is>
+      </c>
+      <c r="Z117" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -10599,6 +11769,16 @@
       <c r="X118" t="n">
         <v>1000</v>
       </c>
+      <c r="Y118" t="inlineStr">
+        <is>
+          <t>csp</t>
+        </is>
+      </c>
+      <c r="Z118" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -10685,6 +11865,16 @@
       <c r="X119" t="n">
         <v>1000</v>
       </c>
+      <c r="Y119" t="inlineStr">
+        <is>
+          <t>csp</t>
+        </is>
+      </c>
+      <c r="Z119" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -10771,6 +11961,16 @@
       <c r="X120" t="n">
         <v>1000</v>
       </c>
+      <c r="Y120" t="inlineStr">
+        <is>
+          <t>csp</t>
+        </is>
+      </c>
+      <c r="Z120" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -10857,6 +12057,16 @@
       <c r="X121" t="n">
         <v>1000</v>
       </c>
+      <c r="Y121" t="inlineStr">
+        <is>
+          <t>csp</t>
+        </is>
+      </c>
+      <c r="Z121" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -10943,6 +12153,16 @@
       <c r="X122" t="n">
         <v>1000</v>
       </c>
+      <c r="Y122" t="inlineStr">
+        <is>
+          <t>csp</t>
+        </is>
+      </c>
+      <c r="Z122" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -11029,6 +12249,16 @@
       <c r="X123" t="n">
         <v>1000</v>
       </c>
+      <c r="Y123" t="inlineStr">
+        <is>
+          <t>csp</t>
+        </is>
+      </c>
+      <c r="Z123" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -11115,6 +12345,16 @@
       <c r="X124" t="n">
         <v>1000</v>
       </c>
+      <c r="Y124" t="inlineStr">
+        <is>
+          <t>csp</t>
+        </is>
+      </c>
+      <c r="Z124" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -11201,6 +12441,16 @@
       <c r="X125" t="n">
         <v>1000</v>
       </c>
+      <c r="Y125" t="inlineStr">
+        <is>
+          <t>csp</t>
+        </is>
+      </c>
+      <c r="Z125" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -11287,6 +12537,16 @@
       <c r="X126" t="n">
         <v>1000</v>
       </c>
+      <c r="Y126" t="inlineStr">
+        <is>
+          <t>csp</t>
+        </is>
+      </c>
+      <c r="Z126" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -11373,6 +12633,16 @@
       <c r="X127" t="n">
         <v>1000</v>
       </c>
+      <c r="Y127" t="inlineStr">
+        <is>
+          <t>csp</t>
+        </is>
+      </c>
+      <c r="Z127" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -11459,6 +12729,16 @@
       <c r="X128" t="n">
         <v>1000</v>
       </c>
+      <c r="Y128" t="inlineStr">
+        <is>
+          <t>csp</t>
+        </is>
+      </c>
+      <c r="Z128" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -11545,6 +12825,16 @@
       <c r="X129" t="n">
         <v>1000</v>
       </c>
+      <c r="Y129" t="inlineStr">
+        <is>
+          <t>csp</t>
+        </is>
+      </c>
+      <c r="Z129" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -11631,6 +12921,16 @@
       <c r="X130" t="n">
         <v>1000</v>
       </c>
+      <c r="Y130" t="inlineStr">
+        <is>
+          <t>csp</t>
+        </is>
+      </c>
+      <c r="Z130" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -11717,6 +13017,16 @@
       <c r="X131" t="n">
         <v>1000</v>
       </c>
+      <c r="Y131" t="inlineStr">
+        <is>
+          <t>csp</t>
+        </is>
+      </c>
+      <c r="Z131" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -11803,6 +13113,16 @@
       <c r="X132" t="n">
         <v>1000</v>
       </c>
+      <c r="Y132" t="inlineStr">
+        <is>
+          <t>csp</t>
+        </is>
+      </c>
+      <c r="Z132" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -11889,6 +13209,16 @@
       <c r="X133" t="n">
         <v>1000</v>
       </c>
+      <c r="Y133" t="inlineStr">
+        <is>
+          <t>csp</t>
+        </is>
+      </c>
+      <c r="Z133" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -11975,6 +13305,16 @@
       <c r="X134" t="n">
         <v>1000</v>
       </c>
+      <c r="Y134" t="inlineStr">
+        <is>
+          <t>csp</t>
+        </is>
+      </c>
+      <c r="Z134" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -12061,6 +13401,16 @@
       <c r="X135" t="n">
         <v>1000</v>
       </c>
+      <c r="Y135" t="inlineStr">
+        <is>
+          <t>csp</t>
+        </is>
+      </c>
+      <c r="Z135" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -12147,6 +13497,16 @@
       <c r="X136" t="n">
         <v>1000</v>
       </c>
+      <c r="Y136" t="inlineStr">
+        <is>
+          <t>csp</t>
+        </is>
+      </c>
+      <c r="Z136" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -12233,6 +13593,16 @@
       <c r="X137" t="n">
         <v>1000</v>
       </c>
+      <c r="Y137" t="inlineStr">
+        <is>
+          <t>csp</t>
+        </is>
+      </c>
+      <c r="Z137" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -12319,6 +13689,16 @@
       <c r="X138" t="n">
         <v>1000</v>
       </c>
+      <c r="Y138" t="inlineStr">
+        <is>
+          <t>csp</t>
+        </is>
+      </c>
+      <c r="Z138" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -12405,6 +13785,16 @@
       <c r="X139" t="n">
         <v>1000</v>
       </c>
+      <c r="Y139" t="inlineStr">
+        <is>
+          <t>csp</t>
+        </is>
+      </c>
+      <c r="Z139" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -12491,6 +13881,16 @@
       <c r="X140" t="n">
         <v>1000</v>
       </c>
+      <c r="Y140" t="inlineStr">
+        <is>
+          <t>csp</t>
+        </is>
+      </c>
+      <c r="Z140" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -12577,6 +13977,16 @@
       <c r="X141" t="n">
         <v>1000</v>
       </c>
+      <c r="Y141" t="inlineStr">
+        <is>
+          <t>csp</t>
+        </is>
+      </c>
+      <c r="Z141" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -12663,6 +14073,16 @@
       <c r="X142" t="n">
         <v>1000</v>
       </c>
+      <c r="Y142" t="inlineStr">
+        <is>
+          <t>csp</t>
+        </is>
+      </c>
+      <c r="Z142" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -12749,6 +14169,16 @@
       <c r="X143" t="n">
         <v>1000</v>
       </c>
+      <c r="Y143" t="inlineStr">
+        <is>
+          <t>csp</t>
+        </is>
+      </c>
+      <c r="Z143" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -12835,6 +14265,16 @@
       <c r="X144" t="n">
         <v>1000</v>
       </c>
+      <c r="Y144" t="inlineStr">
+        <is>
+          <t>csp</t>
+        </is>
+      </c>
+      <c r="Z144" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -12921,6 +14361,16 @@
       <c r="X145" t="n">
         <v>1000</v>
       </c>
+      <c r="Y145" t="inlineStr">
+        <is>
+          <t>csp</t>
+        </is>
+      </c>
+      <c r="Z145" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -13007,6 +14457,16 @@
       <c r="X146" t="n">
         <v>1000</v>
       </c>
+      <c r="Y146" t="inlineStr">
+        <is>
+          <t>csp</t>
+        </is>
+      </c>
+      <c r="Z146" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -13093,6 +14553,16 @@
       <c r="X147" t="n">
         <v>1000</v>
       </c>
+      <c r="Y147" t="inlineStr">
+        <is>
+          <t>csp</t>
+        </is>
+      </c>
+      <c r="Z147" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -13179,6 +14649,16 @@
       <c r="X148" t="n">
         <v>1000</v>
       </c>
+      <c r="Y148" t="inlineStr">
+        <is>
+          <t>csp</t>
+        </is>
+      </c>
+      <c r="Z148" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -13265,6 +14745,16 @@
       <c r="X149" t="n">
         <v>1000</v>
       </c>
+      <c r="Y149" t="inlineStr">
+        <is>
+          <t>csp</t>
+        </is>
+      </c>
+      <c r="Z149" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -13351,6 +14841,16 @@
       <c r="X150" t="n">
         <v>1000</v>
       </c>
+      <c r="Y150" t="inlineStr">
+        <is>
+          <t>csp</t>
+        </is>
+      </c>
+      <c r="Z150" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -13437,6 +14937,16 @@
       <c r="X151" t="n">
         <v>1000</v>
       </c>
+      <c r="Y151" t="inlineStr">
+        <is>
+          <t>csp</t>
+        </is>
+      </c>
+      <c r="Z151" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -13523,6 +15033,16 @@
       <c r="X152" t="n">
         <v>1000</v>
       </c>
+      <c r="Y152" t="inlineStr">
+        <is>
+          <t>csp</t>
+        </is>
+      </c>
+      <c r="Z152" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -13609,6 +15129,16 @@
       <c r="X153" t="n">
         <v>1000</v>
       </c>
+      <c r="Y153" t="inlineStr">
+        <is>
+          <t>csp</t>
+        </is>
+      </c>
+      <c r="Z153" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -13695,6 +15225,16 @@
       <c r="X154" t="n">
         <v>1000</v>
       </c>
+      <c r="Y154" t="inlineStr">
+        <is>
+          <t>csp</t>
+        </is>
+      </c>
+      <c r="Z154" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -13781,6 +15321,16 @@
       <c r="X155" t="n">
         <v>1000</v>
       </c>
+      <c r="Y155" t="inlineStr">
+        <is>
+          <t>csp</t>
+        </is>
+      </c>
+      <c r="Z155" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -13867,6 +15417,16 @@
       <c r="X156" t="n">
         <v>1000</v>
       </c>
+      <c r="Y156" t="inlineStr">
+        <is>
+          <t>csp</t>
+        </is>
+      </c>
+      <c r="Z156" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -13953,6 +15513,16 @@
       <c r="X157" t="n">
         <v>1000</v>
       </c>
+      <c r="Y157" t="inlineStr">
+        <is>
+          <t>csp</t>
+        </is>
+      </c>
+      <c r="Z157" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -14039,6 +15609,16 @@
       <c r="X158" t="n">
         <v>1000</v>
       </c>
+      <c r="Y158" t="inlineStr">
+        <is>
+          <t>csp</t>
+        </is>
+      </c>
+      <c r="Z158" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -14125,6 +15705,16 @@
       <c r="X159" t="n">
         <v>1000</v>
       </c>
+      <c r="Y159" t="inlineStr">
+        <is>
+          <t>csp</t>
+        </is>
+      </c>
+      <c r="Z159" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -14211,6 +15801,16 @@
       <c r="X160" t="n">
         <v>1000</v>
       </c>
+      <c r="Y160" t="inlineStr">
+        <is>
+          <t>csp</t>
+        </is>
+      </c>
+      <c r="Z160" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -14297,6 +15897,16 @@
       <c r="X161" t="n">
         <v>1000</v>
       </c>
+      <c r="Y161" t="inlineStr">
+        <is>
+          <t>csp</t>
+        </is>
+      </c>
+      <c r="Z161" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -14383,6 +15993,16 @@
       <c r="X162" t="n">
         <v>1000</v>
       </c>
+      <c r="Y162" t="inlineStr">
+        <is>
+          <t>csp</t>
+        </is>
+      </c>
+      <c r="Z162" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -14469,6 +16089,16 @@
       <c r="X163" t="n">
         <v>1000</v>
       </c>
+      <c r="Y163" t="inlineStr">
+        <is>
+          <t>csp</t>
+        </is>
+      </c>
+      <c r="Z163" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -14555,6 +16185,16 @@
       <c r="X164" t="n">
         <v>1000</v>
       </c>
+      <c r="Y164" t="inlineStr">
+        <is>
+          <t>csp</t>
+        </is>
+      </c>
+      <c r="Z164" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -14641,6 +16281,16 @@
       <c r="X165" t="n">
         <v>1000</v>
       </c>
+      <c r="Y165" t="inlineStr">
+        <is>
+          <t>csp</t>
+        </is>
+      </c>
+      <c r="Z165" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -14727,6 +16377,16 @@
       <c r="X166" t="n">
         <v>1000</v>
       </c>
+      <c r="Y166" t="inlineStr">
+        <is>
+          <t>csp</t>
+        </is>
+      </c>
+      <c r="Z166" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -14813,6 +16473,16 @@
       <c r="X167" t="n">
         <v>1000</v>
       </c>
+      <c r="Y167" t="inlineStr">
+        <is>
+          <t>csp</t>
+        </is>
+      </c>
+      <c r="Z167" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -14899,6 +16569,16 @@
       <c r="X168" t="n">
         <v>1000</v>
       </c>
+      <c r="Y168" t="inlineStr">
+        <is>
+          <t>csp</t>
+        </is>
+      </c>
+      <c r="Z168" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -14984,6 +16664,16 @@
       </c>
       <c r="X169" t="n">
         <v>1000</v>
+      </c>
+      <c r="Y169" t="inlineStr">
+        <is>
+          <t>csp</t>
+        </is>
+      </c>
+      <c r="Z169" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
     </row>
   </sheetData>
